--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104643_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104643_W21.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4289</v>
+        <v>0.4395</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1183</v>
+        <v>1.2694</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6894</v>
+        <v>-0.8299</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.114</v>
+        <v>-0.1202</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1445</v>
+        <v>0.1328</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2585</v>
+        <v>-0.253</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4631</v>
+        <v>1.4427</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3884</v>
+        <v>1.3682</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5771</v>
+        <v>-1.5629</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.244</v>
+        <v>-1.2355</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9039</v>
+        <v>0.9255</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2431</v>
+        <v>0.4202</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.5053</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7766</v>
+        <v>-0.2476</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0537</v>
+        <v>1.977</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8303</v>
+        <v>-2.2245</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.6045</v>
+        <v>-2.651</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2859</v>
+        <v>-0.7146</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.3186</v>
+        <v>-1.9363</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.282</v>
+        <v>2.0934</v>
       </c>
       <c r="K3" t="n">
-        <v>1.368</v>
+        <v>1.0957</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.6501</v>
+        <v>0.9977</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.3224</v>
+        <v>-4.7444</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6539</v>
+        <v>-1.8103</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6685</v>
+        <v>-2.934</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7864</v>
+        <v>0.1043</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3357</v>
+        <v>-0.0678</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4506</v>
+        <v>0.1721</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.1609</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8335</v>
+        <v>-0.5004</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4905</v>
+        <v>1.9414</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.324</v>
+        <v>-2.4418</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.7053</v>
+        <v>-1.598</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0406</v>
+        <v>-1.4567</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7459</v>
+        <v>-0.1413</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1135</v>
+        <v>2.1856</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1909</v>
+        <v>0.5548</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.07729999999999999</v>
+        <v>1.6308</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8188</v>
+        <v>-3.7836</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1503</v>
+        <v>-2.0116</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6685</v>
+        <v>-1.772</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8057</v>
+        <v>-0.4958</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9648</v>
+        <v>-0.2442</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1591</v>
+        <v>-0.2516</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0923</v>
+        <v>-0.9952</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4256</v>
+        <v>-0.1978</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5179</v>
+        <v>-0.7974</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6459</v>
+        <v>-3.5967</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7055</v>
+        <v>-0.2762</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.9405</v>
+        <v>-3.3204</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1264</v>
+        <v>-0.2997</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1216</v>
+        <v>1.3617</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0048</v>
+        <v>-1.6614</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.7724</v>
+        <v>-3.297</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.827</v>
+        <v>-1.638</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.9453</v>
+        <v>-1.659</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2683</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7373</v>
+        <v>0.5527</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6593</v>
+        <v>0.1019</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.078</v>
+        <v>0.4509</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1568</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06419999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>E. QUINTELA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2038</v>
+        <v>-1.7629</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3688</v>
+        <v>-1.8429</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5727</v>
+        <v>0.0799</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6142</v>
+        <v>0.3124</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4677</v>
+        <v>0.5744</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1466</v>
+        <v>-0.262</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2036</v>
+        <v>1.5438</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5643</v>
+        <v>0.948</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6392</v>
+        <v>0.5958</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.8178</v>
+        <v>-1.2314</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.032</v>
+        <v>-0.3736</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7858</v>
+        <v>-0.8578</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1774</v>
+        <v>0.4286</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8347</v>
+        <v>0.0278</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3427</v>
+        <v>0.4008</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6054</v>
+        <v>-1.8141</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4478</v>
+        <v>0.1862</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0531</v>
+        <v>-2.0003</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2754</v>
+        <v>-0.2781</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4171</v>
+        <v>1.4078</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6926</v>
+        <v>-1.686</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5785</v>
+        <v>2.5598</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5038</v>
+        <v>2.4854</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8539</v>
+        <v>-2.838</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7672</v>
+        <v>-1.7604</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2144</v>
+        <v>0.0104</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1603</v>
+        <v>-0.0746</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0541</v>
+        <v>0.0849</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.1568</v>
+        <v>-1.1609</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. QUINTELA</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0274</v>
+        <v>-2.1018</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0617</v>
+        <v>0.6304</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0343</v>
+        <v>-2.7323</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3078</v>
+        <v>-1.7118</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5743</v>
+        <v>0.0293</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2665</v>
+        <v>-1.7412</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5495</v>
+        <v>1.0825</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9524</v>
+        <v>1.1646</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5971</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2417</v>
+        <v>-2.7943</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3781</v>
+        <v>-1.1353</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8636</v>
+        <v>-1.659</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.4952</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>0.16</v>
+        <v>-0.4599</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2087</v>
+        <v>0.1414</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3687</v>
+        <v>-0.6012</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.835</v>
+        <v>-2.8361</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4608</v>
+        <v>-1.5174</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3742</v>
+        <v>-1.3188</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2663</v>
+        <v>-0.2832</v>
       </c>
       <c r="H9" t="n">
-        <v>0.752</v>
+        <v>0.7388</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0183</v>
+        <v>-1.022</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9635</v>
+        <v>1.9243</v>
       </c>
       <c r="K9" t="n">
-        <v>1.745</v>
+        <v>1.7162</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2185</v>
+        <v>0.2081</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2298</v>
+        <v>-2.2075</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1001</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4053</v>
+        <v>0.4085</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5054</v>
+        <v>-0.4771</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4552</v>
+        <v>-3.4957</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3832</v>
+        <v>0.295</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.072</v>
+        <v>-3.7907</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4328</v>
+        <v>-2.425</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1401</v>
+        <v>-1.132</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2928</v>
+        <v>-1.293</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5214</v>
+        <v>1.5008</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1834</v>
+        <v>0.1756</v>
       </c>
       <c r="L10" t="n">
-        <v>1.338</v>
+        <v>1.3252</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.9542</v>
+        <v>-3.9258</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3234</v>
+        <v>-1.3077</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.6308</v>
+        <v>-2.6182</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5933</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7289</v>
+        <v>-0.019</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.6176</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.1511</v>
+        <v>-8.4499</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9446</v>
+        <v>-4.0807</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.2065</v>
+        <v>-4.3692</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.5208</v>
+        <v>-7.5114</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.3146</v>
+        <v>-3.3062</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.2062</v>
+        <v>-4.2051</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6925</v>
+        <v>-2.7076</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1571</v>
+        <v>-1.1656</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.8283</v>
+        <v>-4.8037</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.1575</v>
+        <v>-2.1406</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.6708</v>
+        <v>-2.6631</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1766</v>
+        <v>-0.4833</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1179</v>
+        <v>-0.2349</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0587</v>
+        <v>-0.2483</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.598</v>
+        <v>-10.3895</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9655</v>
+        <v>-5.87</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.6325</v>
+        <v>-4.5194</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.5163</v>
+        <v>-6.5137</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.0374</v>
+        <v>-4.0381</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.4789</v>
+        <v>-2.4756</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.0015</v>
+        <v>-3.0151</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.2898</v>
+        <v>-2.3</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.5148</v>
+        <v>-3.4986</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.7476</v>
+        <v>-1.7381</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7672</v>
+        <v>-1.7604</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9475</v>
+        <v>-0.7376</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6956</v>
+        <v>-0.5786</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2519</v>
+        <v>-0.159</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-32.1494</v>
+        <v>-32.1537</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.911099999999998</v>
+        <v>-7.2094</v>
       </c>
       <c r="F13" t="n">
-        <v>-25.2383</v>
+        <v>-24.9444</v>
       </c>
       <c r="G13" t="n">
-        <v>-26.3877</v>
+        <v>-26.3767</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.0227</v>
+        <v>-8.040700000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-18.3654</v>
+        <v>-18.3359</v>
       </c>
       <c r="J13" t="n">
-        <v>8.543499999999998</v>
+        <v>8.310500000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>7.570900000000002</v>
+        <v>7.404599999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9722999999999997</v>
+        <v>0.9059</v>
       </c>
       <c r="M13" t="n">
-        <v>-34.9312</v>
+        <v>-34.6872</v>
       </c>
       <c r="N13" t="n">
-        <v>-15.5935</v>
+        <v>-15.4456</v>
       </c>
       <c r="O13" t="n">
-        <v>-19.3376</v>
+        <v>-19.2415</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.670899999999998</v>
+        <v>-5.6907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-18.1468</v>
+        <v>-18.2107</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4756</v>
+        <v>12.5196</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8618000000000002</v>
+        <v>-0.8603000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1358999999999999</v>
+        <v>-0.1193</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7259999999999998</v>
+        <v>-0.7408</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7711999999999999</v>
+        <v>0.7738</v>
       </c>
       <c r="W13" t="n">
-        <v>2.8283</v>
+        <v>2.81</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.057</v>
+        <v>-2.0362</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.5014</v>
+        <v>7.7106</v>
       </c>
       <c r="E14" t="n">
-        <v>5.117</v>
+        <v>5.6737</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3843</v>
+        <v>2.0368</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1514</v>
+        <v>6.1455</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3664</v>
+        <v>2.3666</v>
       </c>
       <c r="I14" t="n">
-        <v>3.785</v>
+        <v>3.7789</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9645</v>
+        <v>4.9382</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5341</v>
+        <v>1.5201</v>
       </c>
       <c r="L14" t="n">
-        <v>3.4304</v>
+        <v>3.4181</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1869</v>
+        <v>1.2073</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8324</v>
+        <v>0.8465</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3726</v>
+        <v>0.5878</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3297</v>
+        <v>0.2622</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7023</v>
+        <v>0.3256</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W14" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.3919</v>
+        <v>7.3285</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3163</v>
+        <v>5.8793</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0755</v>
+        <v>1.4492</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2373</v>
+        <v>6.4784</v>
       </c>
       <c r="H15" t="n">
-        <v>7.1169</v>
+        <v>2.8175</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8796</v>
+        <v>3.6608</v>
       </c>
       <c r="J15" t="n">
-        <v>6.3003</v>
+        <v>5.8447</v>
       </c>
       <c r="K15" t="n">
-        <v>6.7882</v>
+        <v>2.3302</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4878</v>
+        <v>3.5145</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.063</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3288</v>
+        <v>0.4873</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3918</v>
+        <v>0.1463</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4229</v>
+        <v>-0.6538</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8721</v>
+        <v>0.0346</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5507</v>
+        <v>-0.6884</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.4528</v>
+        <v>6.2831</v>
       </c>
       <c r="E16" t="n">
-        <v>3.868</v>
+        <v>4.2104</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5848</v>
+        <v>2.0728</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1555</v>
+        <v>6.2249</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0763</v>
+        <v>7.1007</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0791</v>
+        <v>-0.8757</v>
       </c>
       <c r="J16" t="n">
-        <v>3.499</v>
+        <v>6.2651</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5585</v>
+        <v>6.7568</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9405</v>
+        <v>-0.4917</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6565</v>
+        <v>-0.0402</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5178</v>
+        <v>0.3438</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1387</v>
+        <v>-0.384</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1632</v>
+        <v>1.3345</v>
       </c>
       <c r="T16" t="n">
-        <v>0.369</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7942</v>
+        <v>0.5195</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.0892</v>
+        <v>6.0439</v>
       </c>
       <c r="E17" t="n">
-        <v>5.3285</v>
+        <v>3.6222</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7608</v>
+        <v>2.4217</v>
       </c>
       <c r="G17" t="n">
-        <v>6.4937</v>
+        <v>4.1646</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8181</v>
+        <v>2.0819</v>
       </c>
       <c r="I17" t="n">
-        <v>3.6756</v>
+        <v>2.0826</v>
       </c>
       <c r="J17" t="n">
-        <v>5.8849</v>
+        <v>3.4876</v>
       </c>
       <c r="K17" t="n">
-        <v>2.348</v>
+        <v>1.5513</v>
       </c>
       <c r="L17" t="n">
-        <v>3.537</v>
+        <v>1.9363</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6088</v>
+        <v>0.677</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4701</v>
+        <v>0.5306</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8997</v>
+        <v>0.7411</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5565</v>
+        <v>0.1345</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.3432</v>
+        <v>0.6066</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.4159</v>
+        <v>5.237</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4543</v>
+        <v>3.6369</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9616</v>
+        <v>1.6001</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3445</v>
+        <v>3.3304</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8976</v>
+        <v>0.8907</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4469</v>
+        <v>2.4397</v>
       </c>
       <c r="J18" t="n">
-        <v>5.7842</v>
+        <v>5.7404</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1028</v>
+        <v>3.0747</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6814</v>
+        <v>2.6657</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4397</v>
+        <v>-2.41</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.2052</v>
+        <v>-2.1839</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8586</v>
+        <v>-0.0267</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6079</v>
+        <v>-0.3719</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2507</v>
+        <v>0.3452</v>
       </c>
       <c r="V18" t="n">
-        <v>1.7032</v>
+        <v>1.7057</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1568</v>
+        <v>1.1609</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.1404</v>
+        <v>4.7382</v>
       </c>
       <c r="E19" t="n">
-        <v>1.044</v>
+        <v>1.6132</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0964</v>
+        <v>3.125</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3934</v>
+        <v>3.3977</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9811</v>
+        <v>0.9876</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4123</v>
+        <v>2.4101</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5955</v>
+        <v>2.5773</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3219</v>
+        <v>0.3135</v>
       </c>
       <c r="L19" t="n">
-        <v>2.2736</v>
+        <v>2.2638</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.8204</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1603</v>
+        <v>0.4299</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4174</v>
+        <v>0.174</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2571</v>
+        <v>0.2559</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.351</v>
+        <v>2.2328</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5413</v>
+        <v>1.7557</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1903</v>
+        <v>0.477</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0081</v>
+        <v>0.0191</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.8226</v>
+        <v>-2.8096</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8308</v>
+        <v>2.8287</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1492</v>
+        <v>2.1277</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7588</v>
+        <v>-0.7692</v>
       </c>
       <c r="L20" t="n">
-        <v>2.908</v>
+        <v>2.8968</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.141</v>
+        <v>-2.1086</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0638</v>
+        <v>-2.0405</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1523</v>
+        <v>-0.2903</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6079</v>
+        <v>-0.3719</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5444</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. KEITA</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2403</v>
+        <v>-0.3208</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.789</v>
+        <v>1.5391</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0293</v>
+        <v>-1.8599</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3177</v>
+        <v>0.5457</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5656</v>
+        <v>-1.7554</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2479</v>
+        <v>2.301</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3369</v>
+        <v>3.0282</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4861</v>
+        <v>0.3997</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1493</v>
+        <v>2.6285</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0192</v>
+        <v>-2.4825</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0795</v>
+        <v>-2.1551</v>
       </c>
       <c r="O21" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.3275</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3973</v>
+        <v>-0.1835</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5213</v>
+        <v>-0.3022</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.124</v>
+        <v>0.1187</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>S. KEITA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8053</v>
+        <v>-0.4255</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3386</v>
+        <v>-1.6256</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1439</v>
+        <v>1.2</v>
       </c>
       <c r="G22" t="n">
-        <v>0.546</v>
+        <v>-1.3149</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7649</v>
+        <v>-1.5653</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3109</v>
+        <v>0.2504</v>
       </c>
       <c r="J22" t="n">
-        <v>3.0526</v>
+        <v>-1.3442</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4085</v>
+        <v>-1.4931</v>
       </c>
       <c r="L22" t="n">
-        <v>2.6441</v>
+        <v>0.1489</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5065</v>
+        <v>0.0292</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.1734</v>
+        <v>-0.0722</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3331</v>
+        <v>0.1014</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6708</v>
+        <v>0.7316</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5383</v>
+        <v>0.699</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1325</v>
+        <v>0.0327</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5533</v>
+        <v>-1.6087</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.554</v>
+        <v>-0.4451</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9993</v>
+        <v>-1.1635</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3173</v>
+        <v>-1.3058</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0347</v>
+        <v>-1.0258</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2825</v>
+        <v>-0.2799</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0671</v>
+        <v>1.0625</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9136</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3843</v>
+        <v>-2.3683</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9525</v>
+        <v>-1.9394</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3021</v>
+        <v>-0.3728</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4869</v>
+        <v>-0.3695</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1848</v>
+        <v>-0.0033</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.075</v>
+        <v>-3.4859</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4266</v>
+        <v>-0.9155</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6484</v>
+        <v>-2.5704</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3073</v>
+        <v>-1.3089</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0461</v>
+        <v>-1.0482</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2612</v>
+        <v>-0.2607</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9707</v>
+        <v>0.9596</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8587</v>
+        <v>0.8479</v>
       </c>
       <c r="L24" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.278</v>
+        <v>-2.2684</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.9048</v>
+        <v>-1.8961</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5498</v>
+        <v>0.1416</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5081</v>
+        <v>0.037</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>32.14929999999999</v>
+        <v>33.7332</v>
       </c>
       <c r="E25" t="n">
-        <v>25.2384</v>
+        <v>24.9443</v>
       </c>
       <c r="F25" t="n">
-        <v>6.9108</v>
+        <v>8.788800000000002</v>
       </c>
       <c r="G25" t="n">
-        <v>26.3876</v>
+        <v>26.37669999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>8.022499999999997</v>
+        <v>8.040700000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>18.3652</v>
+        <v>18.3359</v>
       </c>
       <c r="J25" t="n">
-        <v>34.93110000000001</v>
+        <v>34.68710000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>15.5936</v>
+        <v>15.4455</v>
       </c>
       <c r="L25" t="n">
-        <v>19.3378</v>
+        <v>19.2415</v>
       </c>
       <c r="M25" t="n">
-        <v>-8.543200000000001</v>
+        <v>-8.310499999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.5709</v>
+        <v>-7.4049</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9722999999999999</v>
+        <v>-0.9057999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>5.6707</v>
+        <v>5.690599999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.4759</v>
+        <v>-12.5199</v>
       </c>
       <c r="R25" t="n">
-        <v>18.1467</v>
+        <v>18.2105</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8619999999999997</v>
+        <v>2.4394</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7259000000000003</v>
+        <v>0.7407999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1360000000000002</v>
+        <v>1.6987</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.7711999999999999</v>
+        <v>-0.7738999999999998</v>
       </c>
       <c r="W25" t="n">
-        <v>2.057</v>
+        <v>2.036099999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.8283</v>
+        <v>-2.810099999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104643_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104643_W21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-2.0362</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>1.1609</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104643_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-2.810099999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
